--- a/chicago/reference/resident-research/T-0442/T-0442_resident_research_working.xlsx
+++ b/chicago/reference/resident-research/T-0442/T-0442_resident_research_working.xlsx
@@ -2515,7 +2515,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>uncertain (inferred)</t>
+          <t>present (inferred)</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
